--- a/5/search/FY4_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY4_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,37 +492,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>315.8</v>
+        <v>315</v>
       </c>
       <c r="B2" t="n">
-        <v>131.3</v>
+        <v>131.8</v>
       </c>
       <c r="C2" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>12110.7382808572</v>
+        <v>12062.44208086841</v>
       </c>
       <c r="F2" t="n">
-        <v>919.8542195433085</v>
+        <v>937.5579191315883</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>13052.04190870228</v>
+        <v>12994.40881847228</v>
       </c>
       <c r="I2" t="n">
-        <v>4.476439495265026</v>
+        <v>5.591181527718618</v>
       </c>
       <c r="J2" t="n">
         <v>1310</v>
       </c>
       <c r="K2" t="n">
-        <v>1.600000000000001</v>
+        <v>1.799999999999997</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -530,37 +530,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>315.8</v>
+        <v>316.6</v>
       </c>
       <c r="B3" t="n">
-        <v>129.3</v>
+        <v>131.8</v>
       </c>
       <c r="C3" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>12130.89780714433</v>
+        <v>12149.1504996077</v>
       </c>
       <c r="F3" t="n">
-        <v>900.2499368510382</v>
+        <v>913.3023929117253</v>
       </c>
       <c r="G3" t="n">
         <v>1800</v>
       </c>
       <c r="H3" t="n">
-        <v>13057.8632228364</v>
+        <v>13106.77591594744</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.184541139914018</v>
+        <v>7.721053671496293</v>
       </c>
       <c r="J3" t="n">
         <v>1310</v>
       </c>
       <c r="K3" t="n">
-        <v>1.099999999999998</v>
+        <v>1.200000000000003</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -568,31 +568,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>315.8</v>
+        <v>315</v>
       </c>
       <c r="B4" t="n">
-        <v>127.3</v>
+        <v>128.8</v>
       </c>
       <c r="C4" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>12149.91027645922</v>
+        <v>12092.90424100193</v>
       </c>
       <c r="F4" t="n">
-        <v>881.7611183233353</v>
+        <v>907.0957589980717</v>
       </c>
       <c r="G4" t="n">
         <v>1800</v>
       </c>
       <c r="H4" t="n">
-        <v>13062.53747999829</v>
+        <v>13003.6577751702</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.730057610525819</v>
+        <v>-3.65777517020183</v>
       </c>
       <c r="J4" t="n">
         <v>1310</v>
@@ -606,10 +606,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>315.8</v>
+        <v>315</v>
       </c>
       <c r="B5" t="n">
-        <v>126.3</v>
+        <v>124.8</v>
       </c>
       <c r="C5" t="n">
         <v>12.6</v>
@@ -618,25 +618,25 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>12140.87720280283</v>
+        <v>12111.91127128022</v>
       </c>
       <c r="F5" t="n">
-        <v>890.5453986193027</v>
+        <v>888.0887287197775</v>
       </c>
       <c r="G5" t="n">
         <v>1800</v>
       </c>
       <c r="H5" t="n">
-        <v>13046.33530026539</v>
+        <v>12994.38053420103</v>
       </c>
       <c r="I5" t="n">
-        <v>10.02587371398715</v>
+        <v>5.619465798965734</v>
       </c>
       <c r="J5" t="n">
         <v>1310</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6000000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -644,37 +644,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>314.2</v>
+        <v>316.6</v>
       </c>
       <c r="B6" t="n">
-        <v>130.3</v>
+        <v>128.8</v>
       </c>
       <c r="C6" t="n">
-        <v>11.4</v>
+        <v>12.6</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>12035.58298708223</v>
+        <v>12179.14350202538</v>
       </c>
       <c r="F6" t="n">
-        <v>935.0866451838194</v>
+        <v>884.9394204657187</v>
       </c>
       <c r="G6" t="n">
         <v>1800</v>
       </c>
       <c r="H6" t="n">
-        <v>12943.98911610172</v>
+        <v>13114.971678236</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9521234152401803</v>
+        <v>-0.02929345037773601</v>
       </c>
       <c r="J6" t="n">
         <v>1310</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4000000000000021</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -682,31 +682,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>317.4</v>
+        <v>316.6</v>
       </c>
       <c r="B7" t="n">
-        <v>130.3</v>
+        <v>132.8</v>
       </c>
       <c r="C7" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>12208.50947569144</v>
+        <v>12157.86939565935</v>
       </c>
       <c r="F7" t="n">
-        <v>888.7185704944009</v>
+        <v>905.0573427820723</v>
       </c>
       <c r="G7" t="n">
         <v>1800</v>
       </c>
       <c r="H7" t="n">
-        <v>13167.64398020845</v>
+        <v>13122.76055870881</v>
       </c>
       <c r="I7" t="n">
-        <v>6.749181997893515</v>
+        <v>-7.394871566200891</v>
       </c>
       <c r="J7" t="n">
         <v>1310</v>
